--- a/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
@@ -42,12 +42,12 @@
     <t xml:space="preserve">Huasco</t>
   </si>
   <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:39</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>108.18</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>87.33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -533,13 +533,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3301</v>
+        <v>3201</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.31</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3201</v>
+        <v>3301</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>77.05</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>77.02</v>
+        <v>81.87</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.98</v>
+        <v>74.63</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>61.17</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>51.67</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46.82</v>
+        <v>49.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:38</t>
+    <t xml:space="preserve">2026-10-05 16:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
